--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1,277 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12900"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24045" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>value_type</t>
-  </si>
-  <si>
-    <t>read_schema_from_file</t>
-  </si>
-  <si>
-    <t>input</t>
-  </si>
-  <si>
-    <t>index</t>
-  </si>
-  <si>
-    <t>mode</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>output</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>记录类名</t>
-  </si>
-  <si>
-    <t>从excel读取定义</t>
-  </si>
-  <si>
-    <t>文件列表</t>
-  </si>
-  <si>
-    <t>表id字段</t>
-  </si>
-  <si>
-    <t>模式</t>
-  </si>
-  <si>
-    <t>分组</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>输出文件名</t>
-  </si>
-  <si>
-    <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
-  </si>
-  <si>
-    <t>可以多个，以逗号','分隔</t>
-  </si>
-  <si>
-    <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
-  </si>
-  <si>
-    <t>取值one|map|list，为空自动为map</t>
-  </si>
-  <si>
-    <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
-  </si>
-  <si>
-    <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
-  </si>
-  <si>
-    <t>item.TbItem</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>item.xlsx</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color theme="0"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -571,161 +471,162 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -779,11 +680,74 @@
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1043,125 +1007,770 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
-    <col min="2" max="2" width="20.3809523809524" customWidth="1"/>
-    <col min="3" max="3" width="15.5714285714286" customWidth="1"/>
-    <col min="4" max="4" width="32.4285714285714" customWidth="1"/>
-    <col min="5" max="5" width="24.3809523809524" customWidth="1"/>
-    <col min="6" max="9" width="18" customWidth="1"/>
+    <col width="20.3809523809524" customWidth="1" style="2" min="2" max="2"/>
+    <col width="15.5714285714286" customWidth="1" style="2" min="3" max="3"/>
+    <col width="32.4285714285714" customWidth="1" style="2" min="4" max="4"/>
+    <col width="24.3809523809524" customWidth="1" style="2" min="5" max="5"/>
+    <col width="18" customWidth="1" style="2" min="6" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" customFormat="1" s="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>value_type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>read_schema_from_file</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" customFormat="1" s="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>全名(包含模块和名字)</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>记录类名</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>从excel读取定义</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>文件列表</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>表id字段</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>模式</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>注释</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>输出文件名</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" customFormat="1" s="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>可以多个，以逗号','分隔</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>取值one|map|list，为空自动为map</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>item.TbItem</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5">
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>item.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>battle.TbUnit</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>unit.xlsx</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>小兵基础配置</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>battle.TbWeaponRegistry</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>WeaponRegistry</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>weapon_registry.xlsx</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>武器符号注册表(逆向快照)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>battle.TbBoss</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>boss.xlsx</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Boss配置</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>battle.TbBuff</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>buff.xlsx</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Buff类型配置</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>battle.TbSkill</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>skill.xlsx</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>技能配置</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>battle.TbEnemy</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>enemy.xlsx</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>敌人类型配置(逆向快照)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>battle.TbGeneral</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>general.xlsx</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>武将配置</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>battle.TbRank</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>rank.xlsx</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>军衔关卡配置</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>battle.TbWeapon</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>weapon.xlsx</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>武器配置(原始)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>battle.TbWeaponText</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>WeaponText</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>weapon_text.xlsx</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>武器名字拆字</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>battle.TbEvent</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>event.xlsx</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>事件名映射</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>battle.TbResultSchema</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ResultSchema</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>result_schema.xlsx</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>战斗结果字段说明</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>battle.TbUnitLevel</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>UnitLevel</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>unit_level.xlsx</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>one</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>小兵等级倍数</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>battle.TbWave</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Wave</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>wave.xlsx</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>one</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>波次配置</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>battle.TbMap</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Map</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>map.xlsx</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>one</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>地图配置</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>battle.TbEconomy</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>economy.xlsx</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>one</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>战斗经济配置</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>battle.TbProjectile</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Projectile</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>projectile.xlsx</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>one</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>弹道类型</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
     <col width="20.3809523809524" customWidth="1" style="2" min="2" max="2"/>
@@ -1189,585 +1189,651 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr"/>
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>battle.TbUnit</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>unit.xlsx</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t>小兵基础配置</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
+      <c r="K5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr"/>
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>battle.TbWeaponRegistry</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>WeaponRegistry</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>weapon_registry.xlsx</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr">
         <is>
           <t>武器符号注册表(逆向快照)</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
+      <c r="K6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr"/>
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>battle.TbBoss</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>boss.xlsx</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr">
         <is>
           <t>Boss配置</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
+      <c r="K7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr"/>
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>battle.TbBuff</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>buff.xlsx</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr">
         <is>
           <t>Buff类型配置</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
+      <c r="K8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr"/>
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>battle.TbSkill</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>Skill</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>skill.xlsx</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr">
         <is>
           <t>技能配置</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
+      <c r="K9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr"/>
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>battle.TbEnemy</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>Enemy</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>enemy.xlsx</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr">
         <is>
           <t>敌人类型配置(逆向快照)</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
+      <c r="K10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr"/>
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>battle.TbGeneral</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>general.xlsx</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr">
         <is>
           <t>武将配置</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
+      <c r="K11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr"/>
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>battle.TbRank</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>rank.xlsx</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr">
         <is>
           <t>军衔关卡配置</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
+      <c r="K12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr"/>
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>battle.TbWeapon</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>Weapon</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>weapon.xlsx</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr">
         <is>
           <t>武器配置(原始)</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
+      <c r="K13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr"/>
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>battle.TbWeaponText</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>WeaponText</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>weapon_text.xlsx</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr">
         <is>
           <t>武器名字拆字</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
+      <c r="K14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr"/>
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>battle.TbEvent</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>event.xlsx</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr">
         <is>
           <t>事件名映射</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
+      <c r="K15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr"/>
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>battle.TbResultSchema</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>ResultSchema</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>result_schema.xlsx</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr">
         <is>
           <t>战斗结果字段说明</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
+      <c r="K16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr"/>
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>battle.TbUnitLevel</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>UnitLevel</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>unit_level.xlsx</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr">
         <is>
           <t>小兵等级倍数</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
+      <c r="K17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr"/>
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>battle.TbWave</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>Wave</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="0" t="inlineStr">
         <is>
           <t>wave.xlsx</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr">
         <is>
           <t>波次配置</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
+      <c r="K18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr"/>
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>battle.TbMap</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>Map</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>map.xlsx</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>mapIndex</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="n"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>地图配置</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr"/>
+      <c r="K19" s="0" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr"/>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>battle.TbEconomy</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>economy.xlsx</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>地图配置</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>battle.TbEconomy</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Economy</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>战斗经济配置</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr"/>
+      <c r="K20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr"/>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>battle.TbProjectile</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Projectile</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>economy.xlsx</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>projectile.xlsx</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>战斗经济配置</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>battle.TbProjectile</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Projectile</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>弹道类型</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr"/>
+      <c r="K21" s="0" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>battle.TbEnemyStats</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>EnemyStats</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>projectile.xlsx</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>one</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>弹道类型</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>enemystats.xlsx</t>
+        </is>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t>enemyKey</t>
+        </is>
+      </c>
+      <c r="G22" s="0" t="inlineStr"/>
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t>敌人运行时数值(公式输入,task 3.1 新增)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>battle.TbDeck</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>Deck</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>deck.xlsx</t>
+        </is>
+      </c>
+      <c r="F23" s="0" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="G23" s="0" t="inlineStr"/>
+      <c r="I23" s="0" t="inlineStr">
+        <is>
+          <t>最简牌组配置(task 3.1 新增,spec 6.5 均匀四兵)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
     <col width="20.3809523809524" customWidth="1" style="2" min="2" max="2"/>
@@ -1835,6 +1835,37 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>battle.TbSoldierVisual</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>SoldierVisual</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>soldier_visual.xlsx</t>
+        </is>
+      </c>
+      <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t>animationKey</t>
+        </is>
+      </c>
+      <c r="G24" s="0" t="inlineStr"/>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t>兵种表现 Profile(美术锚点偏移)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
     <col width="20.3809523809524" customWidth="1" style="2" min="2" max="2"/>
@@ -1846,7 +1846,7 @@
           <t>SoldierVisual</t>
         </is>
       </c>
-      <c r="D24" t="b">
+      <c r="D24" s="0" t="b">
         <v>1</v>
       </c>
       <c r="E24" s="0" t="inlineStr">
@@ -1863,6 +1863,42 @@
       <c r="I24" s="0" t="inlineStr">
         <is>
           <t>兵种表现 Profile(美术锚点偏移)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>battle.TbWavePlan</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>WavePlan</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>wave_plan.xlsx</t>
+        </is>
+      </c>
+      <c r="F25" s="0" t="inlineStr"/>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="inlineStr">
+        <is>
+          <t>波次计划表</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R123885de003e42e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf6fe3668e0b14ee6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -370,22 +370,22 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="49">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="44" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="42" fontId="19" fillId="0" borderId="0" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
@@ -394,7 +394,7 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
@@ -518,7 +518,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -528,6 +528,20 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
@@ -877,651 +891,1029 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
-      <x:c r="A1" s="1" t="str">
-        <x:v>##var</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="str">
-        <x:v>full_name</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="str">
-        <x:v>value_type</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="str">
-        <x:v>read_schema_from_file</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="str">
-        <x:v>input</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="str">
-        <x:v>index</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="str">
-        <x:v>mode</x:v>
-      </x:c>
-      <x:c r="H1" s="1" t="str">
-        <x:v>group</x:v>
-      </x:c>
-      <x:c r="I1" s="1" t="str">
-        <x:v>comment</x:v>
-      </x:c>
-      <x:c r="J1" s="1" t="str">
-        <x:v>tags</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="str">
-        <x:v>output</x:v>
+      <x:c r="A1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">##var</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">full_name</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">value_type</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">read_schema_from_file</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">input</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">index</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">mode</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">group</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">comment</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">tags</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">output</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2" s="1" customFormat="1">
-      <x:c r="A2" s="1" t="str">
-        <x:v>##</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="str">
-        <x:v>全名(包含模块和名字)</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="str">
-        <x:v>记录类名</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="str">
-        <x:v>从excel读取定义</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="str">
-        <x:v>文件列表</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="str">
-        <x:v>表id字段</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="str">
-        <x:v>模式</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="str">
-        <x:v>分组</x:v>
-      </x:c>
-      <x:c r="I2" s="1" t="str">
-        <x:v>注释</x:v>
-      </x:c>
-      <x:c r="J2"/>
-      <x:c r="K2" s="1" t="str">
-        <x:v>输出文件名</x:v>
+      <x:c r="A2" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">##</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">全名(包含模块和名字)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">记录类名</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D2" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">从excel读取定义</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E2" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">文件列表</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F2" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">表id字段</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G2" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">模式</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H2" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">分组</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I2" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">注释</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J2" s="3" t="n"/>
+      <x:c r="K2" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">输出文件名</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1">
-      <x:c r="A3" s="1" t="str">
-        <x:v>##</x:v>
-      </x:c>
-      <x:c r="B3"/>
-      <x:c r="C3"/>
-      <x:c r="D3" s="1" t="str">
-        <x:v>false时取已有定义，true为从excel标题头和属性栏读取定义</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="str">
-        <x:v>可以多个，以逗号','分隔</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="str">
-        <x:v>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="str">
-        <x:v>取值one|map|list，为空自动为map</x:v>
-      </x:c>
-      <x:c r="H3" s="1" t="str">
-        <x:v>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</x:v>
-      </x:c>
-      <x:c r="I3"/>
-      <x:c r="J3"/>
-      <x:c r="K3" s="1" t="str">
-        <x:v>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</x:v>
+      <x:c r="A3" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">##</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="3" t="n"/>
+      <x:c r="C3" s="3" t="n"/>
+      <x:c r="D3" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">false时取已有定义，true为从excel标题头和属性栏读取定义</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E3" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">可以多个，以逗号','分隔</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F3" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G3" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">取值one|map|list，为空自动为map</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H3" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I3" s="3" t="n"/>
+      <x:c r="J3" s="3" t="n"/>
+      <x:c r="K3" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4"/>
-      <x:c r="B4" t="str">
-        <x:v>item.TbItem</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>Item</x:v>
+      <x:c r="A4" s="3" t="n"/>
+      <x:c r="B4" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">item.TbItem</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Item</x:t>
+        </x:is>
       </x:c>
       <x:c r="D4" s="3" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E4" t="str">
-        <x:v>item.xlsx</x:v>
-      </x:c>
-      <x:c r="F4" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G4"/>
-      <x:c r="H4"/>
-      <x:c r="I4"/>
-      <x:c r="J4"/>
-      <x:c r="K4"/>
+      <x:c r="E4" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">item.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F4" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G4" s="3" t="n"/>
+      <x:c r="H4" s="3" t="n"/>
+      <x:c r="I4" s="3" t="n"/>
+      <x:c r="J4" s="3" t="n"/>
+      <x:c r="K4" s="3" t="n"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5"/>
-      <x:c r="B5" t="str">
-        <x:v>battle.TbUnit</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>Unit</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E5" t="str">
-        <x:v>unit.xlsx</x:v>
-      </x:c>
-      <x:c r="F5" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G5"/>
-      <x:c r="H5"/>
-      <x:c r="I5" t="str">
-        <x:v>小兵基础配置</x:v>
-      </x:c>
-      <x:c r="J5"/>
-      <x:c r="K5"/>
+      <x:c r="A5" s="3" t="n"/>
+      <x:c r="B5" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbUnit</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unit</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">True</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E5" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">unit.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F5" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G5" s="3" t="n"/>
+      <x:c r="H5" s="3" t="n"/>
+      <x:c r="I5" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">小兵基础配置</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J5" s="3" t="n"/>
+      <x:c r="K5" s="3" t="n"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6"/>
-      <x:c r="B6" t="str">
-        <x:v>battle.TbWeaponRegistry</x:v>
-      </x:c>
-      <x:c r="C6" t="str">
-        <x:v>WeaponRegistry</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E6" t="str">
-        <x:v>weapon_registry.xlsx</x:v>
-      </x:c>
-      <x:c r="F6" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G6"/>
-      <x:c r="H6"/>
-      <x:c r="I6" t="str">
-        <x:v>武器符号注册表(逆向快照)</x:v>
-      </x:c>
-      <x:c r="J6"/>
-      <x:c r="K6"/>
+      <x:c r="A6" s="3" t="n"/>
+      <x:c r="B6" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbWeaponRegistry</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">WeaponRegistry</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">True</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E6" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">weapon_registry.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F6" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G6" s="3" t="n"/>
+      <x:c r="H6" s="3" t="n"/>
+      <x:c r="I6" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">武器符号注册表(逆向快照)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J6" s="3" t="n"/>
+      <x:c r="K6" s="3" t="n"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7"/>
-      <x:c r="B7" t="str">
-        <x:v>battle.TbBoss</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>Boss</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E7" t="str">
-        <x:v>boss.xlsx</x:v>
-      </x:c>
-      <x:c r="F7" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G7"/>
-      <x:c r="H7"/>
-      <x:c r="I7" t="str">
-        <x:v>Boss配置</x:v>
-      </x:c>
-      <x:c r="J7"/>
-      <x:c r="K7"/>
+      <x:c r="A7" s="3" t="n"/>
+      <x:c r="B7" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbBoss</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Boss</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">True</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E7" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">boss.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F7" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G7" s="3" t="n"/>
+      <x:c r="H7" s="3" t="n"/>
+      <x:c r="I7" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Boss配置</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J7" s="3" t="n"/>
+      <x:c r="K7" s="3" t="n"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8"/>
-      <x:c r="B8" t="str">
-        <x:v>battle.TbBuff</x:v>
-      </x:c>
-      <x:c r="C8" t="str">
-        <x:v>Buff</x:v>
-      </x:c>
-      <x:c r="D8" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E8" t="str">
-        <x:v>buff.xlsx</x:v>
-      </x:c>
-      <x:c r="F8" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G8"/>
-      <x:c r="H8"/>
-      <x:c r="I8" t="str">
-        <x:v>Buff类型配置</x:v>
-      </x:c>
-      <x:c r="J8"/>
-      <x:c r="K8"/>
+      <x:c r="A8" s="3" t="n"/>
+      <x:c r="B8" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbBuff</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Buff</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">True</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E8" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">buff.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F8" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G8" s="3" t="n"/>
+      <x:c r="H8" s="3" t="n"/>
+      <x:c r="I8" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Buff类型配置</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J8" s="3" t="n"/>
+      <x:c r="K8" s="3" t="n"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9"/>
-      <x:c r="B9" t="str">
-        <x:v>battle.TbSkill</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>Skill</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E9" t="str">
-        <x:v>skill.xlsx</x:v>
-      </x:c>
-      <x:c r="F9" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G9"/>
-      <x:c r="H9"/>
-      <x:c r="I9" t="str">
-        <x:v>技能配置</x:v>
-      </x:c>
-      <x:c r="J9"/>
-      <x:c r="K9"/>
+      <x:c r="A9" s="3" t="n"/>
+      <x:c r="B9" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbSkill</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Skill</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">True</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E9" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">skill.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F9" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G9" s="3" t="n"/>
+      <x:c r="H9" s="3" t="n"/>
+      <x:c r="I9" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">技能配置</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J9" s="3" t="n"/>
+      <x:c r="K9" s="3" t="n"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10"/>
-      <x:c r="B10" t="str">
-        <x:v>battle.TbEnemy</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
-        <x:v>Enemy</x:v>
-      </x:c>
-      <x:c r="D10" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E10" t="str">
-        <x:v>enemy.xlsx</x:v>
-      </x:c>
-      <x:c r="F10" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G10"/>
-      <x:c r="H10"/>
-      <x:c r="I10" t="str">
-        <x:v>敌人类型配置(逆向快照)</x:v>
-      </x:c>
-      <x:c r="J10"/>
-      <x:c r="K10"/>
+      <x:c r="A10" s="3" t="n"/>
+      <x:c r="B10" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbEnemy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enemy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">True</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E10" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">enemy.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F10" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G10" s="3" t="n"/>
+      <x:c r="H10" s="3" t="n"/>
+      <x:c r="I10" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">敌人类型配置(逆向快照)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J10" s="3" t="n"/>
+      <x:c r="K10" s="3" t="n"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11"/>
-      <x:c r="B11" t="str">
-        <x:v>battle.TbGeneral</x:v>
-      </x:c>
-      <x:c r="C11" t="str">
-        <x:v>General</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E11" t="str">
-        <x:v>general.xlsx</x:v>
-      </x:c>
-      <x:c r="F11" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G11"/>
-      <x:c r="H11"/>
-      <x:c r="I11" t="str">
-        <x:v>武将配置</x:v>
-      </x:c>
-      <x:c r="J11"/>
-      <x:c r="K11"/>
+      <x:c r="A11" s="3" t="n"/>
+      <x:c r="B11" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbGeneral</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">General</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">True</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E11" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">general.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F11" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G11" s="3" t="n"/>
+      <x:c r="H11" s="3" t="n"/>
+      <x:c r="I11" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">武将配置</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J11" s="3" t="n"/>
+      <x:c r="K11" s="3" t="n"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12"/>
-      <x:c r="B12" t="str">
-        <x:v>battle.TbRank</x:v>
-      </x:c>
-      <x:c r="C12" t="str">
-        <x:v>Rank</x:v>
-      </x:c>
-      <x:c r="D12" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E12" t="str">
-        <x:v>rank.xlsx</x:v>
-      </x:c>
-      <x:c r="F12" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G12"/>
-      <x:c r="H12"/>
-      <x:c r="I12" t="str">
-        <x:v>军衔关卡配置</x:v>
-      </x:c>
-      <x:c r="J12"/>
-      <x:c r="K12"/>
+      <x:c r="A12" s="3" t="n"/>
+      <x:c r="B12" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbRank</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Rank</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">True</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">rank.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F12" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G12" s="3" t="n"/>
+      <x:c r="H12" s="3" t="n"/>
+      <x:c r="I12" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">军衔关卡配置</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J12" s="3" t="n"/>
+      <x:c r="K12" s="3" t="n"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13"/>
-      <x:c r="B13" t="str">
-        <x:v>battle.TbWeapon</x:v>
-      </x:c>
-      <x:c r="C13" t="str">
-        <x:v>Weapon</x:v>
-      </x:c>
-      <x:c r="D13" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E13" t="str">
-        <x:v>weapon.xlsx</x:v>
-      </x:c>
-      <x:c r="F13" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G13"/>
-      <x:c r="H13"/>
-      <x:c r="I13" t="str">
-        <x:v>武器配置(原始)</x:v>
-      </x:c>
-      <x:c r="J13"/>
-      <x:c r="K13"/>
+      <x:c r="A13" s="3" t="n"/>
+      <x:c r="B13" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbWeapon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Weapon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">True</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E13" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">weapon.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F13" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G13" s="3" t="n"/>
+      <x:c r="H13" s="3" t="n"/>
+      <x:c r="I13" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">武器配置(原始)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J13" s="3" t="n"/>
+      <x:c r="K13" s="3" t="n"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14"/>
-      <x:c r="B14" t="str">
-        <x:v>battle.TbWeaponText</x:v>
-      </x:c>
-      <x:c r="C14" t="str">
-        <x:v>WeaponText</x:v>
-      </x:c>
-      <x:c r="D14" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E14" t="str">
-        <x:v>weapon_text.xlsx</x:v>
-      </x:c>
-      <x:c r="F14" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G14"/>
-      <x:c r="H14"/>
-      <x:c r="I14" t="str">
-        <x:v>武器名字拆字</x:v>
-      </x:c>
-      <x:c r="J14"/>
-      <x:c r="K14"/>
+      <x:c r="A14" s="3" t="n"/>
+      <x:c r="B14" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbWeaponText</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">WeaponText</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">True</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E14" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">weapon_text.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F14" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G14" s="3" t="n"/>
+      <x:c r="H14" s="3" t="n"/>
+      <x:c r="I14" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">武器名字拆字</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J14" s="3" t="n"/>
+      <x:c r="K14" s="3" t="n"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15"/>
-      <x:c r="B15" t="str">
-        <x:v>battle.TbEvent</x:v>
-      </x:c>
-      <x:c r="C15" t="str">
-        <x:v>Event</x:v>
-      </x:c>
-      <x:c r="D15" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E15" t="str">
-        <x:v>event.xlsx</x:v>
-      </x:c>
-      <x:c r="F15" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G15"/>
-      <x:c r="H15"/>
-      <x:c r="I15" t="str">
-        <x:v>事件名映射</x:v>
-      </x:c>
-      <x:c r="J15"/>
-      <x:c r="K15"/>
+      <x:c r="A15" s="3" t="n"/>
+      <x:c r="B15" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbEvent</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Event</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">True</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E15" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">event.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F15" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G15" s="3" t="n"/>
+      <x:c r="H15" s="3" t="n"/>
+      <x:c r="I15" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">事件名映射</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J15" s="3" t="n"/>
+      <x:c r="K15" s="3" t="n"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16"/>
-      <x:c r="B16" t="str">
-        <x:v>battle.TbResultSchema</x:v>
-      </x:c>
-      <x:c r="C16" t="str">
-        <x:v>ResultSchema</x:v>
-      </x:c>
-      <x:c r="D16" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E16" t="str">
-        <x:v>result_schema.xlsx</x:v>
-      </x:c>
-      <x:c r="F16" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G16"/>
-      <x:c r="H16"/>
-      <x:c r="I16" t="str">
-        <x:v>战斗结果字段说明</x:v>
-      </x:c>
-      <x:c r="J16"/>
-      <x:c r="K16"/>
+      <x:c r="A16" s="3" t="n"/>
+      <x:c r="B16" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbResultSchema</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C16" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ResultSchema</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D16" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">True</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E16" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_schema.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F16" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G16" s="3" t="n"/>
+      <x:c r="H16" s="3" t="n"/>
+      <x:c r="I16" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">战斗结果字段说明</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J16" s="3" t="n"/>
+      <x:c r="K16" s="3" t="n"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="B17" t="str">
-        <x:v>battle.TbUnitLevel</x:v>
-      </x:c>
-      <x:c r="C17" t="str">
-        <x:v>UnitLevel</x:v>
-      </x:c>
-      <x:c r="D17" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E17" t="str">
-        <x:v>unit_level.xlsx</x:v>
-      </x:c>
-      <x:c r="F17" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G17"/>
-      <x:c r="H17"/>
-      <x:c r="I17" t="str">
-        <x:v>小兵等级倍数</x:v>
-      </x:c>
-      <x:c r="J17"/>
-      <x:c r="K17"/>
+      <x:c r="A17" s="3" t="n"/>
+      <x:c r="B17" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbUnitLevel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C17" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">UnitLevel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">True</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E17" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">unit_level.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F17" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G17" s="3" t="n"/>
+      <x:c r="H17" s="3" t="n"/>
+      <x:c r="I17" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">小兵等级倍数</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J17" s="3" t="n"/>
+      <x:c r="K17" s="3" t="n"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18" t="str">
-        <x:v>battle.TbWave</x:v>
-      </x:c>
-      <x:c r="C18" t="str">
-        <x:v>Wave</x:v>
-      </x:c>
-      <x:c r="D18" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E18" t="str">
-        <x:v>wave.xlsx</x:v>
-      </x:c>
-      <x:c r="F18"/>
-      <x:c r="G18" t="str">
-        <x:v>one</x:v>
-      </x:c>
-      <x:c r="H18"/>
-      <x:c r="I18" t="str">
-        <x:v>波次配置</x:v>
-      </x:c>
-      <x:c r="J18"/>
-      <x:c r="K18"/>
+      <x:c r="A18" s="3" t="n"/>
+      <x:c r="B18" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbWave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C18" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Wave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D18" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">True</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E18" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">wave.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F18" s="3" t="n"/>
+      <x:c r="G18" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">one</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H18" s="3" t="n"/>
+      <x:c r="I18" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">波次配置</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J18" s="3" t="n"/>
+      <x:c r="K18" s="3" t="n"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19"/>
-      <x:c r="B19" t="str">
-        <x:v>battle.TbMap</x:v>
-      </x:c>
-      <x:c r="C19" t="str">
-        <x:v>Map</x:v>
-      </x:c>
-      <x:c r="D19" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E19" t="str">
-        <x:v>map.xlsx</x:v>
-      </x:c>
-      <x:c r="F19" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G19"/>
-      <x:c r="H19"/>
-      <x:c r="I19" t="str">
-        <x:v>地图配置</x:v>
-      </x:c>
-      <x:c r="J19"/>
-      <x:c r="K19"/>
+      <x:c r="A19" s="3" t="n"/>
+      <x:c r="B19" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbMap</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C19" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Map</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D19" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">True</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E19" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">map.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F19" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G19" s="3" t="n"/>
+      <x:c r="H19" s="3" t="n"/>
+      <x:c r="I19" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">地图配置</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J19" s="3" t="n"/>
+      <x:c r="K19" s="3" t="n"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20"/>
-      <x:c r="B20" t="str">
-        <x:v>battle.TbEconomy</x:v>
-      </x:c>
-      <x:c r="C20" t="str">
-        <x:v>Economy</x:v>
-      </x:c>
-      <x:c r="D20" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E20" t="str">
-        <x:v>economy.xlsx</x:v>
-      </x:c>
-      <x:c r="F20"/>
-      <x:c r="G20" t="str">
-        <x:v>one</x:v>
-      </x:c>
-      <x:c r="H20"/>
-      <x:c r="I20" t="str">
-        <x:v>战斗经济配置</x:v>
-      </x:c>
-      <x:c r="J20"/>
-      <x:c r="K20"/>
+      <x:c r="A20" s="3" t="n"/>
+      <x:c r="B20" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbEconomy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C20" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Economy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D20" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">True</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E20" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">economy.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F20" s="3" t="n"/>
+      <x:c r="G20" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">one</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H20" s="3" t="n"/>
+      <x:c r="I20" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">战斗经济配置</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J20" s="3" t="n"/>
+      <x:c r="K20" s="3" t="n"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21"/>
-      <x:c r="B21" t="str">
-        <x:v>battle.TbProjectile</x:v>
-      </x:c>
-      <x:c r="C21" t="str">
-        <x:v>Projectile</x:v>
-      </x:c>
-      <x:c r="D21" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E21" t="str">
-        <x:v>projectile.xlsx</x:v>
-      </x:c>
-      <x:c r="F21"/>
-      <x:c r="G21" t="str">
-        <x:v>one</x:v>
-      </x:c>
-      <x:c r="H21"/>
-      <x:c r="I21" t="str">
-        <x:v>弹道类型</x:v>
-      </x:c>
-      <x:c r="J21"/>
-      <x:c r="K21"/>
+      <x:c r="A21" s="3" t="n"/>
+      <x:c r="B21" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbProjectile</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C21" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Projectile</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D21" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">True</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E21" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">projectile.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F21" s="3" t="n"/>
+      <x:c r="G21" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">one</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H21" s="3" t="n"/>
+      <x:c r="I21" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">弹道类型</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J21" s="3" t="n"/>
+      <x:c r="K21" s="3" t="n"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22"/>
-      <x:c r="B22" t="str">
-        <x:v>battle.TbEnemyStats</x:v>
-      </x:c>
-      <x:c r="C22" t="str">
-        <x:v>EnemyStats</x:v>
-      </x:c>
-      <x:c r="D22" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E22" t="str">
-        <x:v>enemystats.xlsx</x:v>
-      </x:c>
-      <x:c r="F22" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G22"/>
-      <x:c r="H22"/>
-      <x:c r="I22" t="str">
-        <x:v>敌人运行时数值(公式输入,task 3.1 新增)</x:v>
-      </x:c>
-      <x:c r="J22"/>
-      <x:c r="K22"/>
+      <x:c r="A22" s="3" t="n"/>
+      <x:c r="B22" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbEnemyStats</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C22" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EnemyStats</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D22" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">True</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E22" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">enemystats.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F22" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G22" s="3" t="n"/>
+      <x:c r="H22" s="3" t="n"/>
+      <x:c r="I22" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">敌人运行时数值(公式输入,task 3.1 新增)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J22" s="3" t="n"/>
+      <x:c r="K22" s="3" t="n"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23"/>
-      <x:c r="B23" t="str">
-        <x:v>battle.TbDeck</x:v>
-      </x:c>
-      <x:c r="C23" t="str">
-        <x:v>Deck</x:v>
-      </x:c>
-      <x:c r="D23" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E23" t="str">
-        <x:v>deck.xlsx</x:v>
-      </x:c>
-      <x:c r="F23" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G23"/>
-      <x:c r="H23"/>
-      <x:c r="I23" t="str">
-        <x:v>最简牌组配置(task 3.1 新增,spec 6.5 均匀四兵)</x:v>
-      </x:c>
-      <x:c r="J23"/>
-      <x:c r="K23"/>
+      <x:c r="A23" s="3" t="n"/>
+      <x:c r="B23" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbDeck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C23" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Deck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D23" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">True</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E23" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">deck.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F23" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G23" s="3" t="n"/>
+      <x:c r="H23" s="3" t="n"/>
+      <x:c r="I23" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">最简牌组配置(task 3.1 新增,spec 6.5 均匀四兵)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J23" s="3" t="n"/>
+      <x:c r="K23" s="3" t="n"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24"/>
-      <x:c r="B24" t="str">
-        <x:v>battle.TbSoldierVisual</x:v>
-      </x:c>
-      <x:c r="C24" t="str">
-        <x:v>SoldierVisual</x:v>
+      <x:c r="A24" s="3" t="n"/>
+      <x:c r="B24" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbSoldierVisual</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C24" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SoldierVisual</x:t>
+        </x:is>
       </x:c>
       <x:c r="D24" s="3" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E24" t="str">
-        <x:v>soldier_visual.xlsx</x:v>
-      </x:c>
-      <x:c r="F24" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G24"/>
-      <x:c r="H24"/>
-      <x:c r="I24" t="str">
-        <x:v>兵种表现 Profile(美术锚点偏移)</x:v>
-      </x:c>
-      <x:c r="J24"/>
-      <x:c r="K24"/>
+      <x:c r="E24" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">soldier_visual.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F24" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G24" s="3" t="n"/>
+      <x:c r="H24" s="3" t="n"/>
+      <x:c r="I24" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">兵种表现 Profile(美术锚点偏移)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J24" s="3" t="n"/>
+      <x:c r="K24" s="3" t="n"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25"/>
-      <x:c r="B25" t="str">
-        <x:v>battle.TbWavePlan</x:v>
-      </x:c>
-      <x:c r="C25" t="str">
-        <x:v>WavePlan</x:v>
+      <x:c r="A25" s="3" t="n"/>
+      <x:c r="B25" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbWavePlan</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C25" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">WavePlan</x:t>
+        </x:is>
       </x:c>
       <x:c r="D25" s="3" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E25" t="str">
-        <x:v>wave_plan.xlsx</x:v>
-      </x:c>
-      <x:c r="F25" t="str">
-        <x:v>id+order</x:v>
-      </x:c>
-      <x:c r="G25" t="str">
-        <x:v>list</x:v>
-      </x:c>
-      <x:c r="H25" t="str">
+      <x:c r="E25" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">wave_plan.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F25" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id+order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G25" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">list</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H25" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I25" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">波次计划表</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J25" s="3" t="n"/>
+      <x:c r="K25" s="3" t="n"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="B26" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">battle.TbOpponentAiDifficulty</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C26" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">OpponentAiDifficulty</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D26" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E26" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opponent_ai_difficulty.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F26" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G26" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="I26" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">对手AI难度配置</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="5"/>
+      <x:c r="B27" s="5" t="str">
+        <x:v>battle.TbWeaponReward</x:v>
+      </x:c>
+      <x:c r="C27" s="5" t="str">
+        <x:v>WeaponReward</x:v>
+      </x:c>
+      <x:c r="D27" s="6" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E27" s="5" t="str">
+        <x:v>weapon_reward.xlsx</x:v>
+      </x:c>
+      <x:c r="F27" s="5" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G27" s="5"/>
+      <x:c r="H27" s="5" t="str">
         <x:v>c</x:v>
       </x:c>
-      <x:c r="I25" t="str">
-        <x:v>波次计划表</x:v>
-      </x:c>
-      <x:c r="J25"/>
-      <x:c r="K25"/>
+      <x:c r="I27" s="5" t="str">
+        <x:v>武器碎片战斗结算奖励候选</x:v>
+      </x:c>
+      <x:c r="J27" s="5"/>
+      <x:c r="K27" s="5"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
